--- a/data/trans_orig/IP1021_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP1021_2023-Edad-trans_orig.xlsx
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>398</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4540</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7236</t>
+          <t>6880</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2208</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9150</t>
+          <t>8807</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>154759</t>
+          <t>155165</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>158779</t>
+          <t>158901</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>175318</t>
+          <t>175674</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>181326</t>
+          <t>181490</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>332703</t>
+          <t>333046</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>339645</t>
+          <t>339629</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2316</t>
+          <t>2493</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10411</t>
+          <t>10501</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1548</t>
+          <t>1926</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10915</t>
+          <t>11238</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>5898</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17335</t>
+          <t>17709</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>162661</t>
+          <t>162571</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>170756</t>
+          <t>170579</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>201040</t>
+          <t>200717</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>210407</t>
+          <t>210029</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>367692</t>
+          <t>367318</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>379086</t>
+          <t>379129</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11295</t>
+          <t>10974</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10878</t>
+          <t>11198</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6042</t>
+          <t>6156</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18259</t>
+          <t>18536</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>264163</t>
+          <t>264484</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>272512</t>
+          <t>272445</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>294605</t>
+          <t>294285</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>303752</t>
+          <t>303733</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>562681</t>
+          <t>562404</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>574898</t>
+          <t>574784</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8460</t>
+          <t>8534</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20236</t>
+          <t>19397</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7345</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21086</t>
+          <t>20776</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18255</t>
+          <t>17531</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35664</t>
+          <t>35836</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>645104</t>
+          <t>645943</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>656880</t>
+          <t>656806</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>740350</t>
+          <t>740660</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>754323</t>
+          <t>754091</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1391112</t>
+          <t>1390940</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1408521</t>
+          <t>1409245</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1021_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP1021_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -833,74 +833,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>52090</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>61444</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>225</t>
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2275</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5293</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1708</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>398</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4134</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>349</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6880</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>3778</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2224</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8807</t>
+          <t>6723</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>155247</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>152229</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>156796</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,56%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,64%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,54%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>157591</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>155165</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>158901</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>98,93%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,4%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,75%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>179479</t>
+          <t>144015</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>175674</t>
+          <t>141549</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>181490</t>
+          <t>145169</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>337070</t>
+          <t>299261</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>333046</t>
+          <t>296316</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>339629</t>
+          <t>301219</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4241</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1611</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9044</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,53%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5210</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2493</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10501</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,07%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4767</t>
+          <t>5387</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>2359</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11238</t>
+          <t>10621</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>9977</t>
+          <t>9628</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5898</t>
+          <t>5366</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17709</t>
+          <t>16500</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>195328</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>190525</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>197958</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,87%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,47%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>167862</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>162571</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>170579</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>96,99%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>93,93%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,56%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>207188</t>
+          <t>169285</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>200717</t>
+          <t>164051</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>210029</t>
+          <t>172313</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>375050</t>
+          <t>364614</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>367318</t>
+          <t>357742</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>379129</t>
+          <t>368876</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>199569</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>199569</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>199569</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>211955</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>211955</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>211955</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385027</t>
+          <t>374242</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385027</t>
+          <t>374242</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385027</t>
+          <t>374242</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4748</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1806</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11289</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,86%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>6166</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3013</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>10974</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4901</t>
+          <t>6346</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>3297</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11198</t>
+          <t>11700</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>11067</t>
+          <t>11094</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6156</t>
+          <t>6321</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18536</t>
+          <t>18554</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>287897</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>281356</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>290839</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,38%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,14%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,38%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>269292</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>264484</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>272445</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>97,76%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,02%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,91%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>300582</t>
+          <t>250207</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>294285</t>
+          <t>244853</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>303733</t>
+          <t>253256</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>569873</t>
+          <t>538104</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>562404</t>
+          <t>530644</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>574784</t>
+          <t>542877</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11263</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6666</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>19304</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>13084</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>8534</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>19397</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>12743</t>
+          <t>13236</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>8451</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20776</t>
+          <t>20185</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>25827</t>
+          <t>24500</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17531</t>
+          <t>17123</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35836</t>
+          <t>33763</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>689010</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>680969</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>693607</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,39%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,24%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,05%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>920</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>652256</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>645943</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>656806</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>98,03%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,08%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,72%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>961</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>748693</t>
+          <t>615597</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>740660</t>
+          <t>608648</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>754091</t>
+          <t>620382</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1400949</t>
+          <t>1304606</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1390940</t>
+          <t>1295343</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1409245</t>
+          <t>1311983</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700273</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700273</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700273</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761436</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761436</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761436</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1426776</t>
+          <t>1329106</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1426776</t>
+          <t>1329106</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1426776</t>
+          <t>1329106</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
